--- a/week1/week1-个人周报-杨子翔-20260620.xlsx
+++ b/week1/week1-个人周报-杨子翔-20260620.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="22185" windowHeight="9015"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
   <si>
     <t>周报时间：</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>对应的两篇学习笔记</t>
+  </si>
+  <si>
+    <t>优秀</t>
   </si>
   <si>
     <t>学习花书第一部分</t>
@@ -823,7 +826,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -881,9 +884,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -894,12 +894,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -909,18 +903,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -929,14 +911,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1278,7 +1263,7 @@
         <v>1</v>
       </c>
       <c r="K1" s="10"/>
-      <c r="L1" s="32" t="s">
+      <c r="L1" s="20" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="18"/>
@@ -1298,7 +1283,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
-      <c r="M2" s="33"/>
+      <c r="M2" s="26"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="7" t="s">
@@ -1322,10 +1307,10 @@
         <v>8</v>
       </c>
       <c r="K3" s="12"/>
-      <c r="L3" s="34" t="s">
+      <c r="L3" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="34" t="s">
+      <c r="M3" s="27" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1347,40 +1332,46 @@
         <v>13</v>
       </c>
       <c r="I4" s="16"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
+      <c r="J4" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="28"/>
+      <c r="L4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="29" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="13">
         <v>2</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="16"/>
       <c r="F5" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" s="18"/>
       <c r="H5" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="16"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="13">
         <v>3</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
@@ -1390,86 +1381,86 @@
       </c>
       <c r="G6" s="18"/>
       <c r="H6" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6" s="16"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="37"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="13">
         <v>4</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
       <c r="F7" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" s="18"/>
-      <c r="H7" s="19" t="s">
-        <v>16</v>
+      <c r="H7" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="I7" s="16"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="37"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="13">
         <v>5</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
       <c r="F8" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="18"/>
       <c r="H8" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" s="16"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="13">
         <v>6</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
       <c r="E9" s="16"/>
       <c r="F9" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" s="18"/>
       <c r="H9" s="14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I9" s="16"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1481,14 +1472,14 @@
       <c r="I13" s="10"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="19" t="s">
         <v>4</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
+        <v>27</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
       <c r="E14" s="18"/>
       <c r="F14" s="17" t="s">
         <v>6</v>
@@ -1504,7 +1495,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -1523,17 +1514,17 @@
         <v>2</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="16"/>
       <c r="F16" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I16" s="16"/>
     </row>
@@ -1542,17 +1533,17 @@
         <v>3</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="16"/>
       <c r="F17" s="17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I17" s="16"/>
     </row>
@@ -1561,17 +1552,17 @@
         <v>4</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I18" s="16"/>
     </row>
@@ -1579,31 +1570,31 @@
       <c r="A19" s="13">
         <v>5</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="25"/>
-      <c r="H19" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="23"/>
+      <c r="B19" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="22"/>
+      <c r="H19" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="21"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="29"/>
+      <c r="A20" s="23"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="56">

--- a/week1/week1-个人周报-杨子翔-20260620.xlsx
+++ b/week1/week1-个人周报-杨子翔-20260620.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
   <si>
     <t>周报时间：</t>
   </si>
@@ -79,55 +79,67 @@
     <t>学习花书第一部分</t>
   </si>
   <si>
+    <t>6h</t>
+  </si>
+  <si>
+    <t>学完对应的二三四五章</t>
+  </si>
+  <si>
+    <t>第五章还没学完，学完二三四章</t>
+  </si>
+  <si>
+    <t>良好</t>
+  </si>
+  <si>
+    <t>完成基于logistic/softmax regression的分类模型并进行实验分析</t>
+  </si>
+  <si>
+    <t>实验结果及分析、模型代码</t>
+  </si>
+  <si>
+    <t>掌握感知机、BP神经网络</t>
+  </si>
+  <si>
+    <t>5h</t>
+  </si>
+  <si>
+    <t>一篇学习笔记</t>
+  </si>
+  <si>
+    <t>掌握均方误差损失函数(RMSE)</t>
+  </si>
+  <si>
+    <t>2h</t>
+  </si>
+  <si>
+    <t>手动推导BP神经网络的过程（3层）</t>
+  </si>
+  <si>
+    <t>一份推导过程</t>
+  </si>
+  <si>
+    <t>下周工作安排</t>
+  </si>
+  <si>
+    <t>工作计划</t>
+  </si>
+  <si>
+    <t>做新生入门任务指南任务二（视频学习和linux巩固）</t>
+  </si>
+  <si>
+    <t>入门训练计划任务一的收尾（查漏补缺）</t>
+  </si>
+  <si>
     <t>4h</t>
   </si>
   <si>
-    <t>一篇学习笔记</t>
-  </si>
-  <si>
-    <t>完成基于logistic/softmax regression的分类模型并进行实验分析</t>
+    <t>一篇总结笔记</t>
+  </si>
+  <si>
+    <t>完成基于卷积神经网络的图像识别模型并提交结果</t>
   </si>
   <si>
     <t>一篇学习笔记包括实验结果及分析、模型代码</t>
-  </si>
-  <si>
-    <t>掌握感知机、BP神经网络</t>
-  </si>
-  <si>
-    <t>5h</t>
-  </si>
-  <si>
-    <t>掌握均方误差损失函数(RMSE)</t>
-  </si>
-  <si>
-    <t>2h</t>
-  </si>
-  <si>
-    <t>手动推导BP神经网络的过程（3层）</t>
-  </si>
-  <si>
-    <t>一份推导过程</t>
-  </si>
-  <si>
-    <t>下周工作安排</t>
-  </si>
-  <si>
-    <t>工作计划</t>
-  </si>
-  <si>
-    <t>做新生入门任务指南任务二（视频学习和linux巩固）</t>
-  </si>
-  <si>
-    <t>入门训练计划任务一的收尾（查漏补缺）</t>
-  </si>
-  <si>
-    <t>一篇总结笔记</t>
-  </si>
-  <si>
-    <t>完成基于卷积神经网络的图像识别模型并提交结果</t>
-  </si>
-  <si>
-    <t>6h</t>
   </si>
   <si>
     <t>掌握全连接神经网络、卷积神经网络、残差网络</t>
@@ -826,7 +838,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -911,16 +923,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1335,11 +1341,11 @@
       <c r="J4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="28"/>
-      <c r="L4" s="29" t="s">
+      <c r="K4" s="18"/>
+      <c r="L4" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1361,17 +1367,23 @@
         <v>17</v>
       </c>
       <c r="I5" s="16"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
+      <c r="J5" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="29"/>
+      <c r="L5" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="28" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="13">
         <v>3</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
@@ -1381,86 +1393,110 @@
       </c>
       <c r="G6" s="18"/>
       <c r="H6" s="14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I6" s="16"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
+      <c r="J6" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="29"/>
+      <c r="L6" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="28" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="13">
         <v>4</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
       <c r="F7" s="17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G7" s="18"/>
       <c r="H7" s="14" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I7" s="16"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
+      <c r="J7" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="29"/>
+      <c r="L7" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="28" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="13">
         <v>5</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
       <c r="F8" s="17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G8" s="18"/>
       <c r="H8" s="14" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I8" s="16"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
+      <c r="J8" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="29"/>
+      <c r="L8" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="28" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="13">
         <v>6</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
       <c r="E9" s="16"/>
       <c r="F9" s="17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G9" s="18"/>
       <c r="H9" s="14" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I9" s="16"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
+      <c r="J9" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="29"/>
+      <c r="L9" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="28" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1476,7 +1512,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -1495,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -1514,17 +1550,17 @@
         <v>2</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="16"/>
       <c r="F16" s="17" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I16" s="16"/>
     </row>
@@ -1533,17 +1569,17 @@
         <v>3</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="16"/>
       <c r="F17" s="17" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="14" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="I17" s="16"/>
     </row>
@@ -1552,17 +1588,17 @@
         <v>4</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="14" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I18" s="16"/>
     </row>
@@ -1571,17 +1607,17 @@
         <v>5</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C19" s="21"/>
       <c r="D19" s="21"/>
       <c r="E19" s="21"/>
       <c r="F19" s="22" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G19" s="22"/>
       <c r="H19" s="21" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I19" s="21"/>
     </row>
